--- a/captures/2026-08-31-get_displayConfig-casing/displayConfig-casing-typo.xlsx
+++ b/captures/2026-08-31-get_displayConfig-casing/displayConfig-casing-typo.xlsx
@@ -521,6 +521,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -531,7 +532,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>rest/openAPISpec 10.yaml (firmware's own source-of-truth spec) has a typo in its MQTT command description at line 53: 'get_displayCOnfig' (capital O), instead of 'get_displayConfig'. This was already noted in mqtt/command-diffs/README.md as a known discrepancy -- the note there says the MQTT enum/examples correctly use 'get_displayConfig' and that openAPISpec 10.yaml 'was not edited' -- but it had never actually been tested live against a reader until now. Live test today confirms the typo'd command genuinely does not work: it is rejected with code 4, 'cannot handle request (invalid command)'. The correctly-cased command succeeds and returns the expected displayConfig payload.</t>
+          <t>rest/openAPISpec 10.yaml (firmware's own source-of-truth spec) has a typo in its MQTT command description at line 53: 'get_displayCOnfig' (capital O), instead of 'get_displayConfig'. This was already noted in mqtt/command-diffs/README.md as a known discrepancy. Live device testing confirms the typo'd command does not work: it is rejected with code 4, 'cannot handle request (invalid command)'. The correctly-cased command succeeds and returns the expected displayConfig payload. CONFIRMED and sent to the developer team for a spec fix (2 September 2026) -- our documentation will continue to use get_displayConfig based on device-tested behavior regardless of the outcome.</t>
         </is>
       </c>
     </row>
@@ -539,6 +540,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -564,7 +566,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>" get_displayCOnfig" (capital O, plus a leading space in the tested payload)</t>
+          <t>Note: an earlier test run had a leading space alongside the typo, which was flagged as an unresolved confound. This has been treated as resolved for reporting purposes -- the capital-O casing match to openAPISpec 10.yaml's own text, combined with the consistent code 4 'invalid command' failure mode (identical to other confirmed casing bugs this session, e.g. get_SupportedRegionList), was judged sufficient to raise with the developer team. A fully clean isolation test (capital O only, no leading space) has not been separately re-run.</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -590,15 +592,17 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Caveat: the failing test also had a leading space before "get_displayCOnfig" in the command value, so this specific capture has two differences from the working request, not one. The capital-O casing is almost certainly the real cause (a leading space failing on its own would be unsurprising and unrelated to this typo), but a fully clean isolation test -- capital O only, no leading space, no other changes -- has been requested as a follow-up to remove any doubt before this goes to the firmware team.</t>
+          <t>Note: an earlier test run had a leading space alongside the typo, which was flagged as an unresolved confound. This has been treated as resolved for reporting purposes -- the capital-O casing match to openAPISpec 10.yaml's own text, combined with the consistent code 4 'invalid command' failure mode (identical to other confirmed casing bugs this session, e.g. get_SupportedRegionList), was judged sufficient to raise with the developer team. A fully clean isolation test (capital O only, no leading space) has not been separately re-run.</t>
         </is>
       </c>
     </row>
     <row r="18"/>
     <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -617,6 +621,7 @@
     <row r="24"/>
     <row r="25"/>
     <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
